--- a/resources/Лист Microsoft Excel.xlsx
+++ b/resources/Лист Microsoft Excel.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C96B493-4249-44E2-8CB9-8B8912ED8299}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -18,9 +19,566 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="184">
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Базовый минерал</t>
+  </si>
+  <si>
+    <t>ONYX</t>
+  </si>
+  <si>
+    <t>Quartz (Chalcedony)</t>
+  </si>
+  <si>
+    <t>MORION</t>
+  </si>
+  <si>
+    <t>Quartz</t>
+  </si>
+  <si>
+    <t>SCHORL</t>
+  </si>
+  <si>
+    <t>Tourmaline (Schorl)</t>
+  </si>
+  <si>
+    <t>LACE AGATE</t>
+  </si>
+  <si>
+    <t>BLUE JADE</t>
+  </si>
+  <si>
+    <t>Jadeite</t>
+  </si>
+  <si>
+    <t>LAPIS LAZULI</t>
+  </si>
+  <si>
+    <t>Lazurite (rock)</t>
+  </si>
+  <si>
+    <t>PRASE</t>
+  </si>
+  <si>
+    <t>PRASE OPAL</t>
+  </si>
+  <si>
+    <t>Opal</t>
+  </si>
+  <si>
+    <t>BLOODSTONE</t>
+  </si>
+  <si>
+    <t>MOSS AGATE</t>
+  </si>
+  <si>
+    <t>MOSS OPAL</t>
+  </si>
+  <si>
+    <t>VARISCITE</t>
+  </si>
+  <si>
+    <t>Variscite</t>
+  </si>
+  <si>
+    <t>CHRYSOPRASE</t>
+  </si>
+  <si>
+    <t>CHRYSOCOLLA</t>
+  </si>
+  <si>
+    <t>Chrysocolla</t>
+  </si>
+  <si>
+    <t>SARD</t>
+  </si>
+  <si>
+    <t>CARNELIAN</t>
+  </si>
+  <si>
+    <t>BANDED AGATE</t>
+  </si>
+  <si>
+    <t>SARDONYX</t>
+  </si>
+  <si>
+    <t>CHERRY OPAL</t>
+  </si>
+  <si>
+    <t>LAVENDER JADE</t>
+  </si>
+  <si>
+    <t>PINK JADE</t>
+  </si>
+  <si>
+    <t>TUBE AGATE</t>
+  </si>
+  <si>
+    <t>FIRE AGATE</t>
+  </si>
+  <si>
+    <t>PLUME AGATE</t>
+  </si>
+  <si>
+    <t>BROWN JASPER</t>
+  </si>
+  <si>
+    <t>Quartz (Jasper variety)</t>
+  </si>
+  <si>
+    <t>PICTURE JASPER</t>
+  </si>
+  <si>
+    <t>SMOKY QUARTZ</t>
+  </si>
+  <si>
+    <t>WAX OPAL</t>
+  </si>
+  <si>
+    <t>WOOD OPAL</t>
+  </si>
+  <si>
+    <t>AMBER OPAL</t>
+  </si>
+  <si>
+    <t>GOLD OPAL</t>
+  </si>
+  <si>
+    <t>CITRINE</t>
+  </si>
+  <si>
+    <t>YELLOW JASPER</t>
+  </si>
+  <si>
+    <t>TIGEREYE</t>
+  </si>
+  <si>
+    <t>TIGER IRON</t>
+  </si>
+  <si>
+    <t>Rock (Quartz+Hematite+...)</t>
+  </si>
+  <si>
+    <t>SUNSTONE</t>
+  </si>
+  <si>
+    <t>Feldspar (Orthoclase/Oligoclase)</t>
+  </si>
+  <si>
+    <t>RESIN OPAL</t>
+  </si>
+  <si>
+    <t>PYRITE</t>
+  </si>
+  <si>
+    <t>Pyrite</t>
+  </si>
+  <si>
+    <t>CLEAR TOURMALINE</t>
+  </si>
+  <si>
+    <t>Tourmaline (Achroite)</t>
+  </si>
+  <si>
+    <t>GRAY CHALCEDONY</t>
+  </si>
+  <si>
+    <t>DENDRITIC AGATE</t>
+  </si>
+  <si>
+    <t>SHELL OPAL</t>
+  </si>
+  <si>
+    <t>BONE OPAL</t>
+  </si>
+  <si>
+    <t>WHITE CHALCEDONY</t>
+  </si>
+  <si>
+    <t>FORTIFICATION AGATE</t>
+  </si>
+  <si>
+    <t>MILK QUARTZ</t>
+  </si>
+  <si>
+    <t>MOONSTONE</t>
+  </si>
+  <si>
+    <t>Orthoclase</t>
+  </si>
+  <si>
+    <t>WHITE JADE</t>
+  </si>
+  <si>
+    <t>JASPER OPAL</t>
+  </si>
+  <si>
+    <t>PINEAPPLE OPAL</t>
+  </si>
+  <si>
+    <t>ONYX OPAL</t>
+  </si>
+  <si>
+    <t>MILK OPAL</t>
+  </si>
+  <si>
+    <t>PIPE OPAL</t>
+  </si>
+  <si>
+    <t>AVENTURINE</t>
+  </si>
+  <si>
+    <t>TURQUOISE</t>
+  </si>
+  <si>
+    <t>Turquoise</t>
+  </si>
+  <si>
+    <t>QUARTZ_ROSE</t>
+  </si>
+  <si>
+    <t>CRYSTAL_ROCK</t>
+  </si>
+  <si>
+    <t>BLACK ZIRCON</t>
+  </si>
+  <si>
+    <t>Zircon</t>
+  </si>
+  <si>
+    <t>BLACK PYROPE</t>
+  </si>
+  <si>
+    <t>Pyrope (Garnet)</t>
+  </si>
+  <si>
+    <t>MELANITE</t>
+  </si>
+  <si>
+    <t>Andradite (Andradite)</t>
+  </si>
+  <si>
+    <t>INDIGO TOURMALINE</t>
+  </si>
+  <si>
+    <t>Tourmaline</t>
+  </si>
+  <si>
+    <t>BLUE GARNET</t>
+  </si>
+  <si>
+    <t>Garnet (Garnet Group)</t>
+  </si>
+  <si>
+    <t>TSAVORITE</t>
+  </si>
+  <si>
+    <t>Grossular (Garnet)</t>
+  </si>
+  <si>
+    <t>GREEN TOURMALINE</t>
+  </si>
+  <si>
+    <t>DEMANTOID</t>
+  </si>
+  <si>
+    <t>Andradite (Garnet)</t>
+  </si>
+  <si>
+    <t>GREEN ZIRCON</t>
+  </si>
+  <si>
+    <t>GREEN JADE</t>
+  </si>
+  <si>
+    <t>HELIODOR</t>
+  </si>
+  <si>
+    <t>Beryl</t>
+  </si>
+  <si>
+    <t>PERIDOT</t>
+  </si>
+  <si>
+    <t>Olivine (Forsterite)</t>
+  </si>
+  <si>
+    <t>RED ZIRCON</t>
+  </si>
+  <si>
+    <t>RED TOURMALINE</t>
+  </si>
+  <si>
+    <t>RED PYROPE</t>
+  </si>
+  <si>
+    <t>ALMANDINE</t>
+  </si>
+  <si>
+    <t>Almandine (Garnet)</t>
+  </si>
+  <si>
+    <t>RED GROSSULAR</t>
+  </si>
+  <si>
+    <t>PINK TOURMALINE</t>
+  </si>
+  <si>
+    <t>RED BERYL</t>
+  </si>
+  <si>
+    <t>FIRE OPAL</t>
+  </si>
+  <si>
+    <t>RHODOLITE</t>
+  </si>
+  <si>
+    <t>Garnet (Pyrope–Almandine)</t>
+  </si>
+  <si>
+    <t>SPINEL_PURPLE</t>
+  </si>
+  <si>
+    <t>Spinel</t>
+  </si>
+  <si>
+    <t>ALEXANDRITE</t>
+  </si>
+  <si>
+    <t>Chrysoberyl</t>
+  </si>
+  <si>
+    <t>TANZANITE</t>
+  </si>
+  <si>
+    <t>Zoisite</t>
+  </si>
+  <si>
+    <t>MORGANITE</t>
+  </si>
+  <si>
+    <t>VIOLET SPESSARTINE</t>
+  </si>
+  <si>
+    <t>Spessartine (Garnet)</t>
+  </si>
+  <si>
+    <t>PINK GARNET</t>
+  </si>
+  <si>
+    <t>Garnet</t>
+  </si>
+  <si>
+    <t>KUNZITE</t>
+  </si>
+  <si>
+    <t>Spodumene</t>
+  </si>
+  <si>
+    <t>CINNAMON GROSSULAR</t>
+  </si>
+  <si>
+    <t>HONEY YELLOW BERYL</t>
+  </si>
+  <si>
+    <t>JELLY OPAL</t>
+  </si>
+  <si>
+    <t>BROWN ZIRCON</t>
+  </si>
+  <si>
+    <t>YELLOW ZIRCON</t>
+  </si>
+  <si>
+    <t>GOLDEN BERYL</t>
+  </si>
+  <si>
+    <t>YELLOW SPESSARTINE</t>
+  </si>
+  <si>
+    <t>TOPAZ</t>
+  </si>
+  <si>
+    <t>Topaz</t>
+  </si>
+  <si>
+    <t>TOPAZOLITE</t>
+  </si>
+  <si>
+    <t>YELLOW GROSSULAR</t>
+  </si>
+  <si>
+    <t>RUBICELLE</t>
+  </si>
+  <si>
+    <t>CLEAR GARNET</t>
+  </si>
+  <si>
+    <t>Garnet (Andradite-Grossular)</t>
+  </si>
+  <si>
+    <t>GOSHENITE</t>
+  </si>
+  <si>
+    <t>CAT'S EYE</t>
+  </si>
+  <si>
+    <t>Chrysoberyl (Cymophane)</t>
+  </si>
+  <si>
+    <t>CLEAR ZIRCON</t>
+  </si>
+  <si>
+    <t>AMETHYST</t>
+  </si>
+  <si>
+    <t>AQUAMARINE</t>
+  </si>
+  <si>
+    <t>SPINEL_RED</t>
+  </si>
+  <si>
+    <t>CHRYSOBERYL</t>
+  </si>
+  <si>
+    <t>OPAL_PFIRE</t>
+  </si>
+  <si>
+    <t>OPAL_REDFLASH</t>
+  </si>
+  <si>
+    <t>OPAL_BLACK</t>
+  </si>
+  <si>
+    <t>OPAL_WHITE</t>
+  </si>
+  <si>
+    <t>OPAL_CRYSTAL</t>
+  </si>
+  <si>
+    <t>OPAL_CLARO</t>
+  </si>
+  <si>
+    <t>OPAL_LEVIN</t>
+  </si>
+  <si>
+    <t>OPAL_HARLEQUIN</t>
+  </si>
+  <si>
+    <t>OPAL_PINFIRE</t>
+  </si>
+  <si>
+    <t>OPAL_BANDFIRE</t>
+  </si>
+  <si>
+    <t>DIAMOND_LY</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>DIAMOND_FY</t>
+  </si>
+  <si>
+    <t>EMERALD</t>
+  </si>
+  <si>
+    <t>RUBY</t>
+  </si>
+  <si>
+    <t>Corundum (Ruby variety)</t>
+  </si>
+  <si>
+    <t>SAPPHIRE</t>
+  </si>
+  <si>
+    <t>Corundum (Sapphire variety)</t>
+  </si>
+  <si>
+    <t>DIAMOND_CLEAR</t>
+  </si>
+  <si>
+    <t>DIAMOND_RED</t>
+  </si>
+  <si>
+    <t>DIAMOND_GREEN</t>
+  </si>
+  <si>
+    <t>DIAMOND_BLUE</t>
+  </si>
+  <si>
+    <t>DIAMOND_YELLOW</t>
+  </si>
+  <si>
+    <t>DIAMOND_BLACK</t>
+  </si>
+  <si>
+    <t>SAPPHIRE_STAR</t>
+  </si>
+  <si>
+    <t>Corundum (Star Sapphire)</t>
+  </si>
+  <si>
+    <t>RUBY_STAR</t>
+  </si>
+  <si>
+    <t>Corundum (Star Ruby)</t>
+  </si>
+  <si>
+    <t>pllr2</t>
+  </si>
+  <si>
+    <t>crst2-5</t>
+  </si>
+  <si>
+    <t>disc4,crst4</t>
+  </si>
+  <si>
+    <t>всё</t>
+  </si>
+  <si>
+    <t>crst4,disc4</t>
+  </si>
+  <si>
+    <t>crst8-5</t>
+  </si>
+  <si>
+    <t>crst1,disc1-8</t>
+  </si>
+  <si>
+    <t>pllr5,disc5</t>
+  </si>
+  <si>
+    <t>cube,acub,tthr</t>
+  </si>
+  <si>
+    <t>pllr5</t>
+  </si>
+  <si>
+    <t>disc8,pllr2</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Processor</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,13 +586,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,11 +620,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +902,1456 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:C128">
+    <sortCondition ref="A2"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/resources/Лист Microsoft Excel.xlsx
+++ b/resources/Лист Microsoft Excel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C96B493-4249-44E2-8CB9-8B8912ED8299}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3655305-A7E5-495C-B6C7-1453D3FFC6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="183">
   <si>
     <t>Название</t>
   </si>
@@ -565,13 +565,10 @@
     <t>Structure</t>
   </si>
   <si>
-    <t>Processor</t>
-  </si>
-  <si>
-    <t>Color</t>
-  </si>
-  <si>
     <t>d</t>
+  </si>
+  <si>
+    <t>Feature</t>
   </si>
 </sst>
 </file>
@@ -588,24 +585,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -622,7 +612,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -903,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -916,7 +906,7 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -927,13 +917,10 @@
         <v>180</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E1" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>108</v>
       </c>
@@ -944,10 +931,10 @@
         <v>176</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>98</v>
       </c>
@@ -958,10 +945,10 @@
         <v>177</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
@@ -972,10 +959,10 @@
         <v>172</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>137</v>
       </c>
@@ -986,10 +973,10 @@
         <v>174</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>138</v>
       </c>
@@ -1000,10 +987,10 @@
         <v>179</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>69</v>
       </c>
@@ -1014,10 +1001,10 @@
         <v>174</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -1028,7 +1015,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>76</v>
       </c>
@@ -1039,7 +1026,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>74</v>
       </c>
@@ -1050,7 +1037,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -1061,7 +1048,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>82</v>
       </c>
@@ -1072,7 +1059,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,7 +1070,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>57</v>
       </c>
@@ -1094,7 +1081,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>34</v>
       </c>
@@ -1105,7 +1092,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>122</v>
       </c>
@@ -2349,9 +2336,10 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:C128">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C128">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>